--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le manteau. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Papa dit : manteau pour sortir. Manteau à sa place en rentrant. Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
+          <t>Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le manteau. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Manteau pour sortir. Manteau à sa place en rentrant. Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le manteau. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit.
+papa|Manteau pour sortir. Manteau à sa place en rentrant.
+narrateur|Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va dehors. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a pris le manteau pour sortir. En rentrant, elle l'a raccroché. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara pose ses chaussures. Papa ferme la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Sara va dehors. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Sara a pris le manteau pour sortir. En rentrant, elle l'a raccroché. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Sara pose ses chaussures. Papa ferme la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sara prend son manteau</t>
+          <t>Sarah et les clés qui tintent</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah entend les clés de papa. Elle enfile le manteau jaune, marche dans la rue qui sent le pain, rentre, raccroche.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le manteau. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Manteau pour sortir. Manteau à sa place en rentrant. Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
+          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah est dans le hall. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va dehors, papa ? Oui. On va marcher dans la rue. Avant de sortir, on prend le manteau. Papa tend le manteau. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Bravo. Tu as pris ton manteau. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On rentre maintenant. Ils rentrent. Le hall est calme. En rentrant, le manteau va à sa place. Sarah retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Bravo, Sarah. Tu as fait du bon travail. Manteau pour sortir. Manteau à sa place en rentrant. Je l'ai raccroché, papa. Oui. Tu as su.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le manteau. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit.
+          <t>narrateur|Les clés de papa pendent à un clou.
+narrateur|Elles font une petite chanson.
+narrateur|Un foulard dort sur la rampe.
+narrateur|Il est rayé, bleu et blanc.
+narrateur|Sous la porte, un filet d'air froid.
+narrateur|La rue sent déjà le pain.
+papa|Sarah, tu as entendu les clés ?
+enfant-f|Oui, papa. Elles tintent.
+narrateur|En ce moment, Sarah est dans le hall.
+narrateur|Son manteau jaune attend au crochet.
+narrateur|Le tissu est doux comme une couverture.
+enfant-f|On va dehors, papa ?
+papa|Oui. On va marcher dans la rue.
+papa|Avant de sortir, on prend le manteau.
+narrateur|Papa tend le manteau.
+narrateur|Sarah enfile une manche.
+narrateur|Puis l'autre manche.
+narrateur|Le tissu est doux sur ses bras.
+papa|Bravo. Tu as pris ton manteau.
+papa|Tu veux le foulard aussi ?
+enfant-f|Oui. Il est rayé.
+narrateur|Papa noue le foulard tout doux.
+papa|On peut sortir.
+narrateur|Papa ouvre la porte.
+narrateur|L'air de la rue est frais.
+narrateur|Ça sent le pain chaud.
+narrateur|Ils marchent près.
+narrateur|Sarah tient la main de papa.
+enfant-f|J'ai chaud dans le manteau.
+papa|Oui. Parce que tu l'as pris.
+narrateur|Une vitrine brille.
+narrateur|Le pain est derrière la vitre.
+papa|Tu as vu le pain ?
+enfant-f|Il est doré.
+papa|On rentre maintenant.
+narrateur|Ils rentrent.
+narrateur|Le hall est calme.
+papa|En rentrant, le manteau va à sa place.
+narrateur|Sarah retire le manteau.
+narrateur|Elle le pose à sa place.
+narrateur|Elle le raccroche.
+narrateur|Le crochet fait un petit bruit.
+narrateur|Elle pose le foulard sur la rampe.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
 papa|Manteau pour sortir. Manteau à sa place en rentrant.
-narrateur|Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.</t>
+enfant-f|Je l'ai raccroché, papa.
+papa|Oui. Tu as su.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>cles,porte</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sara va dehors. Que prend-elle ?</t>
+          <t>Sarah va dehors. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1563,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sara va dehors. Que prend-elle ?</t>
+          <t>narrateur|Sarah va dehors. Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a pris le manteau pour sortir. En rentrant, elle l'a raccroché. Papa était là.</t>
+          <t>Sarah a pris le manteau jaune. Elle l'a mis pour sortir. La rue sentait le pain. Elle avait chaud. En rentrant, elle l'a raccroché. Bravo. Tu as pris le manteau. Et tu l'as remis au crochet. C'est du bon travail. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1735,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a pris le manteau pour sortir. En rentrant, elle l'a raccroché. Papa était là.</t>
+          <t>narrateur|Sarah a pris le manteau jaune.
+narrateur|Elle l'a mis pour sortir.
+narrateur|La rue sentait le pain.
+narrateur|Elle avait chaud.
+narrateur|En rentrant, elle l'a raccroché.
+papa|Bravo. Tu as pris le manteau.
+papa|Et tu l'as remis au crochet.
+papa|C'est du bon travail.
+enfant-f|Il est à sa place.
+papa|Oui. Avec le foulard sur la rampe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sara pose ses chaussures. Papa ferme la porte.</t>
+          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le manteau attend. Oui. Il attend au crochet. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1908,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sara pose ses chaussures. Papa ferme la porte.</t>
+          <t>narrateur|Sarah pose ses chaussures.
+narrateur|Elles restent près du paillasson.
+papa|Tu as fini de poser tes chaussures ?
+enfant-f|Oui, papa.
+narrateur|Papa ferme la porte.
+narrateur|Le filet d'air s'arrête.
+narrateur|Les clés redeviennent silencieuses.
+papa|On reste au chaud, maintenant.
+enfant-f|Le manteau attend.
+papa|Oui. Il attend au crochet.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1946,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris le manteau pour la rue. En rentrant, je l'ai raccroché. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2086,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai pris le manteau pour la rue.
+enfant-f|En rentrant, je l'ai raccroché.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Le pain sent encore sous la porte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah est dans le hall. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va dehors, papa ? Oui. On va marcher dans la rue. Avant de sortir, on prend le manteau. Papa tend le manteau. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Bravo. Tu as pris ton manteau. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On rentre maintenant. Ils rentrent. Le hall est calme. En rentrant, le manteau va à sa place. Sarah retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Bravo, Sarah. Tu as fait du bon travail. Manteau pour sortir. Manteau à sa place en rentrant. Je l'ai raccroché, papa. Oui. Tu as su.</t>
+          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va dehors, papa ? Oui. On va marcher dans la rue. Avant de sortir, on prend le manteau. Papa tend le manteau. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Bravo. Tu as pris ton manteau. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. En rentrant, le manteau va à sa place. Sarah retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Bravo, Sarah. Tu as fait du bon travail. Avant de sortir, le manteau. En rentrant, on le pose. Je l'ai raccroché, papa. Oui. Tu as su. Sarah touche encore le foulard. Il est un peu froid, maintenant. Tu as fini de poser le foulard ? Oui. Sur la rampe. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
 narrateur|La rue sent déjà le pain.
 papa|Sarah, tu as entendu les clés ?
 enfant-f|Oui, papa. Elles tintent.
-narrateur|En ce moment, Sarah est dans le hall.
+narrateur|En ce moment, Sarah écoute les clés.
 narrateur|Son manteau jaune attend au crochet.
 narrateur|Le tissu est doux comme une couverture.
 enfant-f|On va dehors, papa ?
@@ -1354,11 +1354,15 @@
 narrateur|Sarah tient la main de papa.
 enfant-f|J'ai chaud dans le manteau.
 papa|Oui. Parce que tu l'as pris.
+narrateur|Ils marchent encore un peu.
+narrateur|Un pigeon picore près du trottoir.
+papa|Tu as vu le pigeon ?
+enfant-f|Oui. Il picore.
 narrateur|Une vitrine brille.
 narrateur|Le pain est derrière la vitre.
 papa|Tu as vu le pain ?
 enfant-f|Il est doré.
-papa|On rentre maintenant.
+papa|C'est l'heure de rentrer.
 narrateur|Ils rentrent.
 narrateur|Le hall est calme.
 papa|En rentrant, le manteau va à sa place.
@@ -1369,9 +1373,14 @@
 narrateur|Elle pose le foulard sur la rampe.
 papa|Bravo, Sarah.
 papa|Tu as fait du bon travail.
-papa|Manteau pour sortir. Manteau à sa place en rentrant.
+papa|Avant de sortir, le manteau. En rentrant, on le pose.
 enfant-f|Je l'ai raccroché, papa.
-papa|Oui. Tu as su.</t>
+papa|Oui. Tu as su.
+narrateur|Sarah touche encore le foulard.
+narrateur|Il est un peu froid, maintenant.
+papa|Tu as fini de poser le foulard ?
+enfant-f|Oui. Sur la rampe.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -2113,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2165,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarah et les clés qui tintent</t>
+          <t>Le pain doré de Sarah</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah entend les clés de papa. Elle enfile le manteau jaune, marche dans la rue qui sent le pain, rentre, raccroche.</t>
+          <t>Sarah veut voir le pain doré derrière la vitrine. Les clés tintent. Une manche du manteau jaune est tordue. Papa l'aide. Ils voient le pigeon et le pain. Le foulard et le manteau rentrent à leur place.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va dehors, papa ? Oui. On va marcher dans la rue. Avant de sortir, on prend le manteau. Papa tend le manteau. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Bravo. Tu as pris ton manteau. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. En rentrant, le manteau va à sa place. Sarah retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Bravo, Sarah. Tu as fait du bon travail. Avant de sortir, le manteau. En rentrant, on le pose. Je l'ai raccroché, papa. Oui. Tu as su. Sarah touche encore le foulard. Il est un peu froid, maintenant. Tu as fini de poser le foulard ? Oui. Sur la rampe. Bravo.</t>
+          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va voir le pain, papa ? Oui. On va marcher jusqu'à la vitrine. Papa prend les clés. Sarah avance vers la porte. Papa tend le manteau jaune. Une manche est un peu tordue. Le bras de Sarah ne glisse pas. Ça coince. Attends. Je tiens la manche ouverte. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On le regarde un moment ? Oui. Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain brille comme le soleil. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui. Sur la rampe. Le manteau est au crochet. Oui. Tu as su.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt;. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Papa dit : manteau pour sortir. Manteau à sa place en rentrant. Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va voir le pain, papa ? Oui. On va marcher jusqu'à la vitrine. Papa prend les clés. Sarah avance vers la porte. Papa tend le manteau jaune. Une manche est un peu tordue. Le bras de Sarah ne glisse pas. Ça coince. Attends. Je tiens la manche ouverte. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On le regarde un moment ? Oui. Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain brille comme le soleil. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui. Sur la rampe. Le manteau est au crochet. Oui. Tu as su.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1331,20 +1331,28 @@
 narrateur|Sous la porte, un filet d'air froid.
 narrateur|La rue sent déjà le pain.
 papa|Sarah, tu as entendu les clés ?
-enfant-f|Oui, papa. Elles tintent.
+enfant-f|Oui, papa.
+enfant-f|Elles tintent.
 narrateur|En ce moment, Sarah écoute les clés.
 narrateur|Son manteau jaune attend au crochet.
 narrateur|Le tissu est doux comme une couverture.
-enfant-f|On va dehors, papa ?
-papa|Oui. On va marcher dans la rue.
-papa|Avant de sortir, on prend le manteau.
-narrateur|Papa tend le manteau.
+enfant-f|On va voir le pain, papa ?
+papa|Oui.
+papa|On va marcher jusqu'à la vitrine.
+narrateur|Papa prend les clés.
+narrateur|Sarah avance vers la porte.
+narrateur|Papa tend le manteau jaune.
+narrateur|Une manche est un peu tordue.
+narrateur|Le bras de Sarah ne glisse pas.
+enfant-f|Ça coince.
+papa|Attends.
+papa|Je tiens la manche ouverte.
 narrateur|Sarah enfile une manche.
 narrateur|Puis l'autre manche.
 narrateur|Le tissu est doux sur ses bras.
-papa|Bravo. Tu as pris ton manteau.
 papa|Tu veux le foulard aussi ?
-enfant-f|Oui. Il est rayé.
+enfant-f|Oui.
+enfant-f|Il est rayé.
 narrateur|Papa noue le foulard tout doux.
 papa|On peut sortir.
 narrateur|Papa ouvre la porte.
@@ -1353,34 +1361,35 @@
 narrateur|Ils marchent près.
 narrateur|Sarah tient la main de papa.
 enfant-f|J'ai chaud dans le manteau.
-papa|Oui. Parce que tu l'as pris.
+papa|Oui.
+papa|Parce que tu l'as pris.
 narrateur|Ils marchent encore un peu.
 narrateur|Un pigeon picore près du trottoir.
 papa|Tu as vu le pigeon ?
-enfant-f|Oui. Il picore.
+enfant-f|Oui.
+enfant-f|Il picore.
 narrateur|Une vitrine brille.
 narrateur|Le pain est derrière la vitre.
 papa|Tu as vu le pain ?
 enfant-f|Il est doré.
+papa|On le regarde un moment ?
+enfant-f|Oui.
+narrateur|Sarah pose le front près de la vitre.
+narrateur|La vitre est un peu froide.
+narrateur|Le pain brille comme le soleil.
 papa|C'est l'heure de rentrer.
 narrateur|Ils rentrent.
 narrateur|Le hall est calme.
-papa|En rentrant, le manteau va à sa place.
-narrateur|Sarah retire le manteau.
-narrateur|Elle le pose à sa place.
-narrateur|Elle le raccroche.
+narrateur|Sarah retire le manteau jaune.
+narrateur|Elle le raccroche au crochet.
 narrateur|Le crochet fait un petit bruit.
 narrateur|Elle pose le foulard sur la rampe.
-papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
-papa|Avant de sortir, le manteau. En rentrant, on le pose.
-enfant-f|Je l'ai raccroché, papa.
-papa|Oui. Tu as su.
-narrateur|Sarah touche encore le foulard.
-narrateur|Il est un peu froid, maintenant.
 papa|Tu as fini de poser le foulard ?
-enfant-f|Oui. Sur la rampe.
-papa|Bravo.</t>
+enfant-f|Oui.
+enfant-f|Sur la rampe.
+enfant-f|Le manteau est au crochet.
+papa|Oui.
+papa|Tu as su.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1417,7 +1426,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara va dehors. Que prend-el&lt;emphasis level="moderate"&gt;le&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah va dehors. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1447,7 +1456,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Avant de sortir, que prend Sara ?</t>
+          <t>Avant de sortir, que prend Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1496,7 +1505,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1572,10 +1581,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah va dehors. Que prend-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah va dehors.
+narrateur|Que prend-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1609,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a pris le manteau jaune. Elle l'a mis pour sortir. La rue sentait le pain. Elle avait chaud. En rentrant, elle l'a raccroché. Bravo. Tu as pris le manteau. Et tu l'as remis au crochet. C'est du bon travail. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
+          <t>Sarah a pris le manteau jaune. Elle l'a mis pour la rue. Elle a vu le pain doré. En rentrant, elle a raccroché. Tu as pris le manteau pour sortir. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a pris le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt; pour sortir. En rentrant, elle l'a raccroché. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a pris le manteau jaune. Elle l'a mis pour la rue. Elle a vu le pain doré. En rentrant, elle a raccroché. Tu as pris le manteau pour sortir. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1668,7 +1677,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1745,18 +1754,15 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Sarah a pris le manteau jaune.
-narrateur|Elle l'a mis pour sortir.
-narrateur|La rue sentait le pain.
-narrateur|Elle avait chaud.
-narrateur|En rentrant, elle l'a raccroché.
-papa|Bravo. Tu as pris le manteau.
-papa|Et tu l'as remis au crochet.
-papa|C'est du bon travail.
+narrateur|Elle l'a mis pour la rue.
+narrateur|Elle a vu le pain doré.
+narrateur|En rentrant, elle a raccroché.
+papa|Tu as pris le manteau pour sortir.
 enfant-f|Il est à sa place.
-papa|Oui. Avec le foulard sur la rampe.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.
+papa|Avec le foulard sur la rampe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,12 +1787,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le manteau attend. Oui. Il attend au crochet. Bravo.</t>
+          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le pain était doré. Oui. Et le manteau attend au crochet.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara pose ses chaussures. Papa ferme la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le pain était doré. Oui. Et le manteau attend au crochet.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1849,7 +1855,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1925,12 +1931,11 @@
 narrateur|Le filet d'air s'arrête.
 narrateur|Les clés redeviennent silencieuses.
 papa|On reste au chaud, maintenant.
-enfant-f|Le manteau attend.
-papa|Oui. Il attend au crochet.
-papa|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+enfant-f|Le pain était doré.
+papa|Oui.
+papa|Et le manteau attend au crochet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris le manteau pour la rue. En rentrant, je l'ai raccroché. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
+          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2023,7 +2028,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2095,15 +2100,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai pris le manteau pour la rue.
-enfant-f|En rentrant, je l'ai raccroché.
+          <t>enfant-f|J'ai vu le pain doré.
+enfant-f|J'avais le manteau pour la rue.
 papa|Bravo, Sarah.
 papa|Tu as fait du bon travail.
 narrateur|Le pain sent encore sous la porte.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2202,6 +2206,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -1960,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
+          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Le pain sent encore sous la porte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Tu as fait du bon travail. Le pain sent encore sous la porte. L'histoire est finie.</t>
+          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Le pain sent encore sous la porte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,9 +2103,7 @@
           <t>enfant-f|J'ai vu le pain doré.
 enfant-f|J'avais le manteau pour la rue.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
-narrateur|Le pain sent encore sous la porte.
-narrateur|L'histoire est finie.</t>
+narrateur|Le pain sent encore sous la porte.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2209,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hall puis rue</t>
+          <t>hall, rue, vitrine de la boulangerie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hall, rue, vitrine de la boulangerie</t>
+          <t>hall au clou des clés, rue, vitrine de la boulangerie</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut voir le pain doré derrière la vitrine. Les clés tintent. Une manche du manteau jaune est tordue. Papa l'aide. Ils voient le pigeon et le pain. Le foulard et le manteau rentrent à leur place.</t>
+          <t>Un filet d'air passe sous la porte du hall. Il sent le pain de la rue. Sur le clou, un éclat de clé brille. Sarah veut le pain doré de la vitrine, maintenant. Elle tire le manteau jaune : la manche est à l'envers. Elle refuse de foncer, ouvre la manche, sort. Un cageot bloque la vitrine ; l'éclat de clé montre un trou. Sur la croûte, l'éclat de clé brille. Le manteau rentre au crochet.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va voir le pain, papa ? Oui. On va marcher jusqu'à la vitrine. Papa prend les clés. Sarah avance vers la porte. Papa tend le manteau jaune. Une manche est un peu tordue. Le bras de Sarah ne glisse pas. Ça coince. Attends. Je tiens la manche ouverte. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On le regarde un moment ? Oui. Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain brille comme le soleil. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui. Sur la rampe. Le manteau est au crochet. Oui. Tu as su.</t>
+          <t>Un filet d'air passe sous la porte du hall. Il sent le pain chaud, venu de la rue. Sarah connaît ce hall. Les crochets, la rampe, le clou des clés. Sur le clou, un éclat de clé brille. Les clés tintent, légères. Il brille, papa. Sarah, tu as vu l'éclat ? Oui, sur la petite clé. Le manteau jaune attend au crochet. Le tissu est épais, un peu rêche. Un foulard rayé dort sur la rampe. Il est bleu et blanc. Le carrelage du hall est froid. Sarah, tu sens le pain ? Oui, papa. Je le veux à la vitrine, maintenant ! La vitrine est au bout de la rue. On y va ! On prend le manteau, d'abord. En ce moment, Sarah saisit le manteau jaune. Elle le tire d'un coup, trop vite. Une manche est tordue, à l'envers. Le bras de Sarah ne glisse pas. Ça coince ! Elle tire plus fort. La manche refuse. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les clés de papa pendent à un clou. Elles font une petite chanson. Un foulard dort sur la rampe. Il est rayé, bleu et blanc. Sous la porte, un filet d'air froid. La rue sent déjà le pain. Sarah, tu as entendu les clés ? Oui, papa. Elles tintent. En ce moment, Sarah écoute les clés. Son manteau jaune attend au crochet. Le tissu est doux comme une couverture. On va voir le pain, papa ? Oui. On va marcher jusqu'à la vitrine. Papa prend les clés. Sarah avance vers la porte. Papa tend le manteau jaune. Une manche est un peu tordue. Le bras de Sarah ne glisse pas. Ça coince. Attends. Je tiens la manche ouverte. Sarah enfile une manche. Puis l'autre manche. Le tissu est doux sur ses bras. Tu veux le foulard aussi ? Oui. Il est rayé. Papa noue le foulard tout doux. On peut sortir. Papa ouvre la porte. L'air de la rue est frais. Ça sent le pain chaud. Ils marchent près. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui. Parce que tu l'as pris. Ils marchent encore un peu. Un pigeon picore près du trottoir. Tu as vu le pigeon ? Oui. Il picore. Une vitrine brille. Le pain est derrière la vitre. Tu as vu le pain ? Il est doré. On le regarde un moment ? Oui. Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain brille comme le soleil. C'est l'heure de rentrer. Ils rentrent. Le hall est calme. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui. Sur la rampe. Le manteau est au crochet. Oui. Tu as su.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un filet d'air passe sous la porte du hall. Il sent le pain chaud, venu de la rue. Sarah connaît ce hall. Les crochets, la rampe, le clou des clés. Sur le clou, un &lt;emphasis level="moderate"&gt;éclat de clé&lt;/emphasis&gt; brille. Les clés tintent, légères. Il brille, papa. Sarah, tu as vu l'éclat ? Oui, sur la petite clé. Le manteau jaune attend au crochet. Le tissu est épais, un peu rêche. Un foulard rayé dort sur la rampe. Il est bleu et blanc. Le carrelage du hall est froid. Sarah, tu sens le pain ? Oui, papa. Je le veux à la vitrine, maintenant ! La vitrine est au bout de la rue. On y va ! On prend le manteau, d'abord. En ce moment, Sarah saisit le manteau jaune. Elle le tire d'un coup, trop vite. Une manche est tordue, à l'envers. Le bras de Sarah ne glisse pas. Ça coince ! Elle tire plus fort. La manche refuse. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sara veut sortir avec papa. Ils sont dans le hall. L'air de la porte est frais. Papa prend le &lt;emphasis&gt;manteau&lt;/emphasis&gt;. Sara enfile le manteau. Le tissu est doux. Ils sortent. La rue sent le pain. Parce qu'elle a le manteau, Sara a chaud. Ils marchent près. Puis ils rentrent. Sara retire le manteau. Elle le pose à sa place. Elle le raccroche. Le crochet fait un petit bruit. Papa dit : manteau pour sortir. Manteau à sa place en rentrant. Sara hoche la tête. Elle a su prendre le manteau. Elle a su le raccrocher. [pause]</t>
+          <t>Un filet d'air passe sous la porte du hall. Il sent le pain chaud, venu de la rue. Sarah connaît ce hall. Les crochets, la rampe, le clou des clés. Sur le clou, un &lt;emphasis&gt;éclat de clé&lt;/emphasis&gt; brille. Les clés tintent, légères. Il brille, papa. Sarah, tu as vu l'éclat ? Oui, sur la petite clé. Le manteau jaune attend au crochet. Le tissu est épais, un peu rêche. Un foulard rayé dort sur la rampe. Il est bleu et blanc. Le carrelage du hall est froid. Sarah, tu sens le pain ? Oui, papa. Je le veux à la vitrine, maintenant ! La vitrine est au bout de la rue. On y va ! On prend le manteau, d'abord. En ce moment, Sarah saisit le manteau jaune. Elle le tire d'un coup, trop vite. Une manche est tordue, à l'envers. Le bras de Sarah ne glisse pas. Ça coince ! Elle tire plus fort. La manche refuse. Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>manteau</t>
+          <t>éclat de clé</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,75 +1321,42 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_le_pain_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les clés de papa pendent à un clou.
-narrateur|Elles font une petite chanson.
-narrateur|Un foulard dort sur la rampe.
-narrateur|Il est rayé, bleu et blanc.
-narrateur|Sous la porte, un filet d'air froid.
-narrateur|La rue sent déjà le pain.
-papa|Sarah, tu as entendu les clés ?
+          <t>narrateur|Un filet d'air passe sous la porte du hall.
+narrateur|Il sent le pain chaud, venu de la rue.
+narrateur|Sarah connaît ce hall.
+narrateur|Les crochets, la rampe, le clou des clés.
+narrateur|Sur le clou, un éclat de clé brille.
+narrateur|Les clés tintent, légères.
+enfant-f|Il brille, papa.
+papa|Sarah, tu as vu l'éclat ?
+enfant-f|Oui, sur la petite clé.
+narrateur|Le manteau jaune attend au crochet.
+narrateur|Le tissu est épais, un peu rêche.
+narrateur|Un foulard rayé dort sur la rampe.
+narrateur|Il est bleu et blanc.
+narrateur|Le carrelage du hall est froid.
+papa|Sarah, tu sens le pain ?
 enfant-f|Oui, papa.
-enfant-f|Elles tintent.
-narrateur|En ce moment, Sarah écoute les clés.
-narrateur|Son manteau jaune attend au crochet.
-narrateur|Le tissu est doux comme une couverture.
-enfant-f|On va voir le pain, papa ?
-papa|Oui.
-papa|On va marcher jusqu'à la vitrine.
-narrateur|Papa prend les clés.
-narrateur|Sarah avance vers la porte.
-narrateur|Papa tend le manteau jaune.
-narrateur|Une manche est un peu tordue.
+enfant-f|Je le veux à la vitrine, maintenant !
+papa|La vitrine est au bout de la rue.
+enfant-f|On y va !
+papa|On prend le manteau, d'abord.
+narrateur|En ce moment, Sarah saisit le manteau jaune.
+narrateur|Elle le tire d'un coup, trop vite.
+narrateur|Une manche est tordue, à l'envers.
 narrateur|Le bras de Sarah ne glisse pas.
-enfant-f|Ça coince.
-papa|Attends.
-papa|Je tiens la manche ouverte.
-narrateur|Sarah enfile une manche.
-narrateur|Puis l'autre manche.
-narrateur|Le tissu est doux sur ses bras.
-papa|Tu veux le foulard aussi ?
-enfant-f|Oui.
-enfant-f|Il est rayé.
-narrateur|Papa noue le foulard tout doux.
-papa|On peut sortir.
-narrateur|Papa ouvre la porte.
-narrateur|L'air de la rue est frais.
-narrateur|Ça sent le pain chaud.
-narrateur|Ils marchent près.
-narrateur|Sarah tient la main de papa.
-enfant-f|J'ai chaud dans le manteau.
-papa|Oui.
-papa|Parce que tu l'as pris.
-narrateur|Ils marchent encore un peu.
-narrateur|Un pigeon picore près du trottoir.
-papa|Tu as vu le pigeon ?
-enfant-f|Oui.
-enfant-f|Il picore.
-narrateur|Une vitrine brille.
-narrateur|Le pain est derrière la vitre.
-papa|Tu as vu le pain ?
-enfant-f|Il est doré.
-papa|On le regarde un moment ?
-enfant-f|Oui.
-narrateur|Sarah pose le front près de la vitre.
-narrateur|La vitre est un peu froide.
-narrateur|Le pain brille comme le soleil.
-papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent.
-narrateur|Le hall est calme.
-narrateur|Sarah retire le manteau jaune.
-narrateur|Elle le raccroche au crochet.
-narrateur|Le crochet fait un petit bruit.
-narrateur|Elle pose le foulard sur la rampe.
-papa|Tu as fini de poser le foulard ?
-enfant-f|Oui.
-enfant-f|Sur la rampe.
-enfant-f|Le manteau est au crochet.
-papa|Oui.
-papa|Tu as su.</t>
+enfant-f|Ça coince !
+narrateur|Elle tire plus fort.
+narrateur|La manche refuse.
+narrateur|Le sourire de Sarah disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1426,12 +1393,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah va dehors. Que prend-elle ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Que prend-elle ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sara va dehors. Que prend-el&lt;emphasis&gt;le&lt;/emphasis&gt; ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Sarah va &lt;emphasis&gt;dehors&lt;/emphasis&gt;. Que prend-elle ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1441,7 +1408,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le manteau | manteau | elle l'enfile</t>
+          <t>le manteau | manteau | elle l'enfile | le manteau jaune</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1494,7 +1461,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1505,7 +1472,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1520,38 +1487,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>dehors</t>
         </is>
       </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1566,17 +1533,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_prend_le_manteau; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1609,17 +1576,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a pris le manteau jaune. Elle l'a mis pour la rue. Elle a vu le pain doré. En rentrant, elle a raccroché. Tu as pris le manteau pour sortir. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
+          <t>Papa s'accroupit à la même hauteur. Tu regardes la manche ? Je veux le pain, papa. Sarah refuse de tirer plus fort. Elle pose un genou au sol. La manche est plate, à l'envers. Je la tourne. Elle retourne le tissu, sans forcer. Le bras glisse, petit à petit. Elle est ouverte. Merci, Sarah. Elle enfile l'autre manche. Le tissu est chaud sur ses bras. Tu veux le foulard aussi ? Oui, il est rayé. Papa noue le foulard, près du cou. On ouvre la porte ? Oui, papa. Papa ouvre la porte du hall. L'air de la rue est frais. Ça sent le pain chaud. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui, parce que tu l'as pris.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a pris le manteau jaune. Elle l'a mis pour la rue. Elle a vu le pain doré. En rentrant, elle a raccroché. Tu as pris le manteau pour sortir. Il est à sa place. Oui. Avec le foulard sur la rampe.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa s'accroupit à la même hauteur. Tu regardes la &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt; ? Je veux le pain, papa. Sarah refuse de tirer plus fort. Elle pose un genou au sol. La manche est plate, à l'envers. Je la tourne. Elle retourne le tissu, sans forcer. Le bras glisse, petit à petit. Elle est ouverte. Merci, Sarah. Elle enfile l'autre manche. Le tissu est chaud sur ses bras. Tu veux le foulard aussi ? Oui, il est rayé. Papa noue le foulard, près du cou. On ouvre la porte ? Oui, papa. Papa ouvre la porte du hall. L'air de la rue est frais. Ça sent le pain chaud. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui, parce que tu l'as pris.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Sara a pris le &lt;emphasis&gt;manteau&lt;/emphasis&gt; pour sortir. En rentrant, elle l'a raccroché. Papa était là. [pause]</t>
+          <t>Papa s'accroupit à la même hauteur. Tu regardes la &lt;emphasis&gt;manche&lt;/emphasis&gt; ? Je veux le pain, papa. Sarah refuse de tirer plus fort. Elle pose un genou au sol. La manche est plate, à l'envers. Je la tourne. Elle retourne le tissu, sans forcer. Le bras glisse, petit à petit. Elle est ouverte. Merci, Sarah. Elle enfile l'autre manche. Le tissu est chaud sur ses bras. Tu veux le foulard aussi ? Oui, il est rayé. Papa noue le foulard, près du cou. On ouvre la porte ? Oui, papa. Papa ouvre la porte du hall. L'air de la rue est frais. Ça sent le pain chaud. Sarah tient la main de papa. J'ai chaud dans le manteau. Oui, parce que tu l'as pris. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1677,7 +1644,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1700,7 +1667,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>manteau</t>
+          <t>manche</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1714,16 +1681,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1748,19 +1715,40 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=1; destinataire=enfant; sous_texte=elle_ouvre_la_manche_sans_forcer; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a pris le manteau jaune.
-narrateur|Elle l'a mis pour la rue.
-narrateur|Elle a vu le pain doré.
-narrateur|En rentrant, elle a raccroché.
-papa|Tu as pris le manteau pour sortir.
-enfant-f|Il est à sa place.
-papa|Oui.
-papa|Avec le foulard sur la rampe.</t>
+          <t>narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu regardes la manche ?
+enfant-f|Je veux le pain, papa.
+narrateur|Sarah refuse de tirer plus fort.
+narrateur|Elle pose un genou au sol.
+narrateur|La manche est plate, à l'envers.
+enfant-f|Je la tourne.
+narrateur|Elle retourne le tissu, sans forcer.
+narrateur|Le bras glisse, petit à petit.
+enfant-f|Elle est ouverte.
+papa|Merci, Sarah.
+narrateur|Elle enfile l'autre manche.
+narrateur|Le tissu est chaud sur ses bras.
+papa|Tu veux le foulard aussi ?
+enfant-f|Oui, il est rayé.
+narrateur|Papa noue le foulard, près du cou.
+papa|On ouvre la porte ?
+enfant-f|Oui, papa.
+narrateur|Papa ouvre la porte du hall.
+narrateur|L'air de la rue est frais.
+narrateur|Ça sent le pain chaud.
+narrateur|Sarah tient la main de papa.
+enfant-f|J'ai chaud dans le manteau.
+papa|Oui, parce que tu l'as pris.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>manteau,foulard</t>
         </is>
       </c>
     </row>
@@ -1787,17 +1775,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le pain était doré. Oui. Et le manteau attend au crochet.</t>
+          <t>Ils marchent près, sur le trottoir. Le manteau jaune tape contre sa hanche. Je le vois, papa ? Bientôt. Une enseigne claque, plus loin. Le trottoir sent la farine. Je cours jusqu'à la vitrine ! Sarah veut glisser entre un cageot et le mur. Le cageot de sacs bloque le passage. Elle pousse, d'un coup. La manche jaune s'accroche à une latte. Ça tient ! Elle tire. Le cageot penche un peu. Sarah s'arrête net. Je n'aime pas ça. Elle refuse de foncer. Attends, je regarde. Papa ne parle pas. Sarah observe les clés, puis le cageot. Dans la main de papa, les clés tintent. L'éclat de clé brille dans un trou, à droite. Par là, papa. Tu vois le trou ? Oui, l'éclat le montre. Ils contournent le cageot, sans se presser. La vitrine est libre. Le pain doré attend derrière le verre. Il est là. Oui, il est près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose ses chaussures. Elles restent près du paillasson. Tu as fini de poser tes chaussures ? Oui, papa. Papa ferme la porte. Le filet d'air s'arrête. Les clés redeviennent silencieuses. On reste au chaud, maintenant. Le pain était doré. Oui. Et le manteau attend au crochet.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils marchent près, sur le trottoir. Le manteau jaune tape contre sa hanche. Je le vois, papa ? Bientôt. Une enseigne claque, plus loin. Le trottoir sent la farine. Je cours jusqu'à la vitrine ! Sarah veut glisser entre un cageot et le mur. Le cageot de sacs bloque le passage. Elle pousse, d'un coup. La manche jaune s'accroche à une latte. Ça tient ! Elle tire. Le cageot penche un peu. Sarah s'arrête net. Je n'aime pas ça. Elle refuse de foncer. Attends, je regarde. Papa ne parle pas. Sarah observe les clés, puis le cageot. Dans la main de papa, les clés tintent. L'&lt;emphasis level="moderate"&gt;éclat de clé&lt;/emphasis&gt; brille dans un trou, à droite. Par là, papa. Tu vois le trou ? Oui, l'éclat le montre. Ils contournent le cageot, sans se presser. La vitrine est libre. Le pain doré attend derrière le verre. Il est là. Oui, il est près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Sara pose ses chaussures. Papa ferme la porte. [pause]</t>
+          <t>Ils marchent près, sur le trottoir. Le manteau jaune tape contre sa hanche. Je le vois, papa ? Bientôt. Une enseigne claque, plus loin. Le trottoir sent la farine. Je cours jusqu'à la vitrine ! Sarah veut glisser entre un cageot et le mur. Le cageot de sacs bloque le passage. Elle pousse, d'un coup. La manche jaune s'accroche à une latte. Ça tient ! Elle tire. Le cageot penche un peu. Sarah s'arrête net. Je n'aime pas ça. Elle refuse de foncer. Attends, je regarde. Papa ne parle pas. Sarah observe les clés, puis le cageot. Dans la main de papa, les clés tintent. L'&lt;emphasis&gt;éclat de clé&lt;/emphasis&gt; brille dans un trou, à droite. Par là, papa. Tu vois le trou ? Oui, l'éclat le montre. Ils contournent le cageot, sans se presser. La vitrine est libre. Le pain doré attend derrière le verre. Il est là. Oui, il est près. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1844,7 +1832,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1852,10 +1840,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1876,28 +1864,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de clé</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1906,10 +1898,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1920,20 +1912,48 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=élan puis prudence puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_l_éclat_montre_le_trou; tempo=vif puis posé; sourire=léger; respiration=relâchée</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sarah pose ses chaussures.
-narrateur|Elles restent près du paillasson.
-papa|Tu as fini de poser tes chaussures ?
-enfant-f|Oui, papa.
-narrateur|Papa ferme la porte.
-narrateur|Le filet d'air s'arrête.
-narrateur|Les clés redeviennent silencieuses.
-papa|On reste au chaud, maintenant.
-enfant-f|Le pain était doré.
-papa|Oui.
-papa|Et le manteau attend au crochet.</t>
+          <t>narrateur|Ils marchent près, sur le trottoir.
+narrateur|Le manteau jaune tape contre sa hanche.
+enfant-f|Je le vois, papa ?
+papa|Bientôt.
+narrateur|Une enseigne claque, plus loin.
+narrateur|Le trottoir sent la farine.
+enfant-f|Je cours jusqu'à la vitrine !
+narrateur|Sarah veut glisser entre un cageot et le mur.
+narrateur|Le cageot de sacs bloque le passage.
+narrateur|Elle pousse, d'un coup.
+narrateur|La manche jaune s'accroche à une latte.
+enfant-f|Ça tient !
+narrateur|Elle tire.
+narrateur|Le cageot penche un peu.
+narrateur|Sarah s'arrête net.
+enfant-f|Je n'aime pas ça.
+narrateur|Elle refuse de foncer.
+enfant-f|Attends, je regarde.
+narrateur|Papa ne parle pas.
+narrateur|Sarah observe les clés, puis le cageot.
+narrateur|Dans la main de papa, les clés tintent.
+narrateur|L'éclat de clé brille dans un trou, à droite.
+enfant-f|Par là, papa.
+papa|Tu vois le trou ?
+enfant-f|Oui, l'éclat le montre.
+narrateur|Ils contournent le cageot, sans se presser.
+narrateur|La vitrine est libre.
+narrateur|Le pain doré attend derrière le verre.
+enfant-f|Il est là.
+papa|Oui, il est près.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>rue,pas</t>
         </is>
       </c>
     </row>
@@ -1960,17 +1980,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Le pain sent encore sous la porte.</t>
+          <t>Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain est doré. Oui, il est chaud. Papa tient les clés contre le verre. Sur la croûte, un éclat de clé brille. Comme sur le clou, papa ! Tu le vois, toi ? Oui, il est sur le pain. Ils rentrent vers le hall. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui, sur la rampe. Les clés retrouvent le clou. Le pain sent sous la porte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le pain doré. J'avais le manteau pour la rue. Bravo, Sarah. Le pain sent encore sous la porte.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain est doré. Oui, il est chaud. Papa tient les clés contre le verre. Sur la croûte, un &lt;emphasis level="moderate"&gt;éclat de clé&lt;/emphasis&gt; brille. Comme sur le clou, papa ! Tu le vois, toi ? Oui, il est sur le pain. Ils rentrent vers le hall. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui, sur la rampe. Les clés retrouvent le clou. Le pain sent sous la porte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sarah pose le front près de la vitre. La vitre est un peu froide. Le pain est doré. Oui, il est chaud. Papa tient les clés contre le verre. Sur la croûte, un &lt;emphasis&gt;éclat de clé&lt;/emphasis&gt; brille. Comme sur le clou, papa ! Tu le vois, toi ? Oui, il est sur le pain. Ils rentrent vers le hall. Sarah retire le manteau jaune. Elle le raccroche au crochet. Le crochet fait un petit bruit. Elle pose le foulard sur la rampe. Tu as fini de poser le foulard ? Oui, sur la rampe. Les clés retrouvent le clou. Le pain sent sous la porte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2017,7 +2037,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2025,7 +2045,7 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2037,12 +2057,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2051,17 +2071,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de clé</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2070,11 +2094,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2083,27 +2107,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_éclat_du_clou_est_sur_la_croute; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai vu le pain doré.
-enfant-f|J'avais le manteau pour la rue.
-papa|Bravo, Sarah.
-narrateur|Le pain sent encore sous la porte.</t>
+          <t>narrateur|Sarah pose le front près de la vitre.
+narrateur|La vitre est un peu froide.
+enfant-f|Le pain est doré.
+papa|Oui, il est chaud.
+narrateur|Papa tient les clés contre le verre.
+narrateur|Sur la croûte, un éclat de clé brille.
+enfant-f|Comme sur le clou, papa !
+papa|Tu le vois, toi ?
+enfant-f|Oui, il est sur le pain.
+narrateur|Ils rentrent vers le hall.
+narrateur|Sarah retire le manteau jaune.
+narrateur|Elle le raccroche au crochet.
+narrateur|Le crochet fait un petit bruit.
+narrateur|Elle pose le foulard sur la rampe.
+papa|Tu as fini de poser le foulard ?
+enfant-f|Oui, sur la rampe.
+narrateur|Les clés retrouvent le clou.
+narrateur|Le pain sent sous la porte.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>vitrine,cles</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2216,6 +2263,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
